--- a/data/trans_bre/IP16A06-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A06-Estudios-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 2,74</t>
+          <t>-17,39; 4,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 17,16</t>
+          <t>-2,77; 17,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,25</t>
+          <t>0,0; 17,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 3,18</t>
+          <t>-3,65; 3,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,65</t>
+          <t>-2,18; 2,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 0,51</t>
+          <t>-3,38; 0,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 0,0</t>
+          <t>-8,14; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 0,0</t>
+          <t>-8,77; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,27 +874,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 2,01</t>
+          <t>-3,18; 2,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,44</t>
+          <t>-1,83; 2,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,84</t>
+          <t>-2,28; 0,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 312,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,44; 558,63</t>
+          <t>-83,14; 631,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A06-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A06-Estudios-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,39; 4,56</t>
+          <t>-18,35; 2,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 17,8</t>
+          <t>-2,75; 18,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,58</t>
+          <t>0,0; 20,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 3,25</t>
+          <t>-3,53; 3,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 2,14</t>
+          <t>-2,6; 1,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,84</t>
+          <t>-3,71; 0,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 0,0</t>
+          <t>-8,39; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 0,0</t>
+          <t>-8,71; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,27 +874,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,05</t>
+          <t>-3,19; 2,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,34</t>
+          <t>-1,95; 2,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,95</t>
+          <t>-2,96; 0,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 306,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-83,14; 631,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A06-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A06-Estudios-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes</t>
+          <t>Menores que consumieron  tranquilizantes, relajantes</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 2,79</t>
+          <t>-17,83; 2,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 18,94</t>
+          <t>-2,7; 17,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,15</t>
+          <t>0,0; 17,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,64</t>
+          <t>-3,56; 3,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,75</t>
+          <t>-2,22; 1,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 0,51</t>
+          <t>-3,69; 0,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 0,0</t>
+          <t>-6,65; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 0,0</t>
+          <t>-10,32; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,27 +874,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,03</t>
+          <t>-3,06; 2,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,55</t>
+          <t>-1,71; 2,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,93</t>
+          <t>-2,63; 0,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 306,28</t>
+          <t>-100,0; 312,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,44; 558,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A06-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A06-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,34 +603,24 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-3,91</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5,69</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,27</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-59,07%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>214,06%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>-0.8877474513475689</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.607882748466546</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.039388105888118</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-0.5742745503441138</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>2.267051165865156</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -629,204 +628,116 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-17,83; 2,74</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-2,7; 17,16</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 17,25</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.557565417687625</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-0.6988667656570796</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.155450047524067</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5.462288265459839</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5.249762038906368</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,38</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-16,11%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-34,73%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-60,19%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,56; 3,18</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,22; 1,65</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,69; 0,51</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.04498989356595206</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.0896849494821806</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.1374096610736298</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.1147033140771095</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.3313778146948366</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.5533356070630433</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,6</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,71</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.6206899723357989</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.5454634469102305</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.7527154484035223</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,65; 0,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-10,32; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.7161187072886611</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.5407756711540188</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1469905340056778</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,77 +745,135 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,61</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-27,35%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-44,08%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.4227961643017146</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.3444009466788789</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,06; 2,01</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,71; 2,44</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,63; 0,84</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 312,5</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-86,44; 558,63</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
+        <v>-2.093706176328161</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.74319000340403</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.1451189252417448</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.05936327681129246</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.08764357085712167</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.3260486221014327</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1671062990092418</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3510836635274259</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.6595455339760341</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.4078125480561379</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.5044808826335896</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="n">
+        <v>-0.868450821258523</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.32618020309727</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.6560561005056098</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.2525372458998866</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="n">
+        <v>6.741124165460175</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -913,12 +882,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
